--- a/manuscript_material/supplementary/Supplementary_Tables.xlsx
+++ b/manuscript_material/supplementary/Supplementary_Tables.xlsx
@@ -565,7 +565,7 @@
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Table numbers match the citations in the Results text: 24 of 67 tables are cited there. Tables marked "not cited in Results" should be cited in the Methods or removed before submission. The last column gives a renumbering in order of first citation, if the journal requires it (edit CITE_ORDER in scripts/make_supplement.py, then update the text citations). Terminology follows the Glossary sheet; archived cell values are unchanged.</t>
+          <t>Table numbers match the citations in the Results text: 25 of 67 tables are cited there. Tables marked "not cited in Results" should be cited in the Methods or removed before submission. The last column gives a renumbering in order of first citation, if the journal requires it (edit CITE_ORDER in scripts/make_supplement.py, then update the text citations). Terminology follows the Glossary sheet; archived cell values are unchanged.</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Section 3: IWC within-set output-agreement ranges</t>
+          <t>Section 3: IWC split sets (Fig. 4a; first cited there by Results_text_edits.md, section C) and within-set output-agreement ranges</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -964,39 +964,43 @@
         </is>
       </c>
       <c r="H14" s="5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>X19</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>X19</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>Task origin, recorded helper exposure and detected tool use</t>
         </is>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="E15" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F15" s="5" t="inlineStr"/>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>not cited in Results</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="n">
-        <v>26</v>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Section 2: domain-tool share of IWC Galaxy analysis jobs (added by Results_text_edits.md, edit 5)</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="16">
@@ -1100,7 +1104,7 @@
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19">
@@ -1300,7 +1304,7 @@
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25">
@@ -1432,7 +1436,7 @@
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29">
@@ -2067,7 +2071,7 @@
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>Section 3: CompBioBench single distinct answer per replicate set (Fig. 4b)</t>
+          <t>Section 3: CompBioBench split replicate sets on the consensus answer (Fig. 4c) and single distinct answer per replicate set</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
@@ -2076,7 +2080,7 @@
         </is>
       </c>
       <c r="H48" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="49">
@@ -2176,7 +2180,7 @@
         </is>
       </c>
       <c r="H51" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="52">
@@ -2203,7 +2207,7 @@
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>Section 3: divergence mechanisms (Fig. 4c; Extended Data Fig. 5a)</t>
+          <t>Section 3: divergence mechanisms (Fig. 4d; Extended Data Fig. 5a)</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
@@ -2212,7 +2216,7 @@
         </is>
       </c>
       <c r="H52" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="53">
@@ -2248,7 +2252,7 @@
         </is>
       </c>
       <c r="H53" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="54">
@@ -2412,7 +2416,7 @@
         </is>
       </c>
       <c r="H58" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="59">
@@ -2471,11 +2475,11 @@
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>Section 3: BixBench-Verified-50 repeatability categories (Fig. 4a,d)</t>
+          <t>Section 3: BixBench-Verified-50 repeatability categories (Fig. 4b,e)</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
@@ -2484,7 +2488,7 @@
         </is>
       </c>
       <c r="H60" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="61">
@@ -4850,6 +4854,11 @@
           <t>All benchmarks</t>
         </is>
       </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>Wrong, scored-incorrect or low-scoring runs in these task cases</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -4874,6 +4883,9 @@
       <c r="F6" s="6" t="n">
         <v>6</v>
       </c>
+      <c r="G6" s="6" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -4898,6 +4910,9 @@
       <c r="F7" s="6" t="n">
         <v>4</v>
       </c>
+      <c r="G7" s="6" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -4922,6 +4937,9 @@
       <c r="F8" s="6" t="n">
         <v>20</v>
       </c>
+      <c r="G8" s="6" t="n">
+        <v>229</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -4946,6 +4964,9 @@
       <c r="F9" s="6" t="n">
         <v>8</v>
       </c>
+      <c r="G9" s="6" t="n">
+        <v>41</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -4970,6 +4991,9 @@
       <c r="F10" s="6" t="n">
         <v>52</v>
       </c>
+      <c r="G10" s="6" t="n">
+        <v>230</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -4994,6 +5018,9 @@
       <c r="F11" s="6" t="n">
         <v>1</v>
       </c>
+      <c r="G11" s="6" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -5018,6 +5045,9 @@
       <c r="F12" s="6" t="n">
         <v>1</v>
       </c>
+      <c r="G12" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -5042,6 +5072,9 @@
       <c r="F13" s="6" t="n">
         <v>1</v>
       </c>
+      <c r="G13" s="6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -5065,6 +5098,9 @@
       </c>
       <c r="F14" s="6" t="n">
         <v>93</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>607</v>
       </c>
     </row>
     <row r="16">
@@ -39378,11 +39414,15 @@
       <c r="C14" s="6" t="n">
         <v>328</v>
       </c>
-      <c r="D14" s="6" t="n"/>
+      <c r="D14" s="6" t="n">
+        <v>293</v>
+      </c>
       <c r="E14" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="F14" s="6" t="n"/>
+      <c r="F14" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -39398,11 +39438,15 @@
       <c r="C15" s="6" t="n">
         <v>328</v>
       </c>
-      <c r="D15" s="6" t="n"/>
+      <c r="D15" s="6" t="n">
+        <v>305</v>
+      </c>
       <c r="E15" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="F15" s="6" t="n"/>
+      <c r="F15" s="6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -39797,11 +39841,15 @@
       <c r="D31" s="6" t="n">
         <v>82</v>
       </c>
-      <c r="E31" s="6" t="n"/>
+      <c r="E31" s="6" t="n">
+        <v>74</v>
+      </c>
       <c r="F31" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="G31" s="6" t="n"/>
+      <c r="G31" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -39822,11 +39870,15 @@
       <c r="D32" s="6" t="n">
         <v>82</v>
       </c>
-      <c r="E32" s="6" t="n"/>
+      <c r="E32" s="6" t="n">
+        <v>79</v>
+      </c>
       <c r="F32" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="G32" s="6" t="n"/>
+      <c r="G32" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -39847,11 +39899,15 @@
       <c r="D33" s="6" t="n">
         <v>82</v>
       </c>
-      <c r="E33" s="6" t="n"/>
+      <c r="E33" s="6" t="n">
+        <v>72</v>
+      </c>
       <c r="F33" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="G33" s="6" t="n"/>
+      <c r="G33" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -39872,11 +39928,15 @@
       <c r="D34" s="6" t="n">
         <v>82</v>
       </c>
-      <c r="E34" s="6" t="n"/>
+      <c r="E34" s="6" t="n">
+        <v>68</v>
+      </c>
       <c r="F34" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="G34" s="6" t="n"/>
+      <c r="G34" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -39897,11 +39957,15 @@
       <c r="D35" s="6" t="n">
         <v>82</v>
       </c>
-      <c r="E35" s="6" t="n"/>
+      <c r="E35" s="6" t="n">
+        <v>79</v>
+      </c>
       <c r="F35" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="G35" s="6" t="n"/>
+      <c r="G35" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -39922,11 +39986,15 @@
       <c r="D36" s="6" t="n">
         <v>82</v>
       </c>
-      <c r="E36" s="6" t="n"/>
+      <c r="E36" s="6" t="n">
+        <v>78</v>
+      </c>
       <c r="F36" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="G36" s="6" t="n"/>
+      <c r="G36" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -39947,11 +40015,15 @@
       <c r="D37" s="6" t="n">
         <v>82</v>
       </c>
-      <c r="E37" s="6" t="n"/>
+      <c r="E37" s="6" t="n">
+        <v>75</v>
+      </c>
       <c r="F37" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="G37" s="6" t="n"/>
+      <c r="G37" s="6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -39972,11 +40044,15 @@
       <c r="D38" s="6" t="n">
         <v>82</v>
       </c>
-      <c r="E38" s="6" t="n"/>
+      <c r="E38" s="6" t="n">
+        <v>73</v>
+      </c>
       <c r="F38" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="G38" s="6" t="n"/>
+      <c r="G38" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -40181,7 +40257,7 @@
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t>d | CompBioBench: distinct answers per replicate set, all 100 tasks (Fig. 4b)</t>
+          <t>d | CompBioBench: distinct answers per replicate set, all 100 tasks</t>
         </is>
       </c>
     </row>
@@ -47336,13 +47412,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
     <col width="29" customWidth="1" min="5" max="5"/>
     <col width="38" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
@@ -47365,7 +47441,7 @@
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>a | Run-level and unanimous accuracy by model configuration (Fig. 4d)</t>
+          <t>a | Run-level and unanimous accuracy by model configuration (Fig. 4e)</t>
         </is>
       </c>
     </row>
@@ -47759,378 +47835,787 @@
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>c | As archived (archive table B2)</t>
+          <t>c | Tasks with no replicate run scored correct (0/3), by execution condition</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Model configuration</t>
+          <t>Execution condition</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Execution condition</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>3/3 scored correct</t>
+          <t>Model configurations with 0/3 replicate runs scored correct (of 5)</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>1-2/3 scored correct</t>
-        </is>
-      </c>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>0/3 scored correct</t>
-        </is>
-      </c>
-      <c r="F23" s="9" t="inlineStr">
-        <is>
-          <t>At least one scored correct</t>
+          <t>Model configurations</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>GPT-5.5</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
+          <t>bix-53-q2</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>5</v>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t>44/50 (88.0%)</t>
+          <t>DeepSeek V4 Pro (Claude Code, superseded); DeepSeek V4 Pro (Codex); GPT-5.5; GPT-5.6 Luna; GPT-5.6 Sol</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>GPT-5.5</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Galaxy</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
+          <t>bix-61-q5</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>5</v>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>45/50 (90.0%)</t>
+          <t>DeepSeek V4 Pro (Claude Code, superseded); DeepSeek V4 Pro (Codex); GPT-5.5; GPT-5.6 Luna; GPT-5.6 Sol</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
+          <t>bix-26-q5</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>4</v>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>45/50 (90.0%)</t>
+          <t>DeepSeek V4 Pro (Codex); GPT-5.5; GPT-5.6 Luna; GPT-5.6 Sol</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Galaxy</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
+          <t>bix-54-q7</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>4</v>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>45/50 (90.0%)</t>
+          <t>DeepSeek V4 Pro (Claude Code, superseded); GPT-5.5; GPT-5.6 Luna; GPT-5.6 Sol</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
+          <t>bix-43-q2</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>3</v>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>46/50 (92.0%)</t>
+          <t>DeepSeek V4 Pro (Claude Code, superseded); DeepSeek V4 Pro (Codex); GPT-5.5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Galaxy</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
+          <t>bix-30-q3</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>2</v>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>45/50 (90.0%)</t>
+          <t>DeepSeek V4 Pro (Codex); GPT-5.6 Sol</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Pro (Codex)</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
+          <t>bix-45-q1</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>2</v>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="F30" s="6" t="inlineStr">
-        <is>
-          <t>43/50 (86.0%)</t>
+          <t>DeepSeek V4 Pro (Claude Code, superseded); GPT-5.5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Pro (Codex)</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Galaxy</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
+          <t>bix-12-q4</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F31" s="6" t="inlineStr">
-        <is>
-          <t>45/50 (90.0%)</t>
+          <t>DeepSeek V4 Pro (Claude Code, superseded)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Pro (Claude Code, superseded)</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+          <t>bix-14-q1</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t>42/50 (84.0%)</t>
+          <t>DeepSeek V4 Pro (Codex)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>bix-31-q2</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
           <t>DeepSeek V4 Pro (Claude Code, superseded)</t>
         </is>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>bix-32-q2</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Codex)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>bix-34-q5</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Claude Code, superseded)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>bix-45-q1</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Claude Code, superseded); DeepSeek V4 Pro (Codex); GPT-5.5; GPT-5.6 Luna; GPT-5.6 Sol</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>bix-53-q2</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Claude Code, superseded); DeepSeek V4 Pro (Codex); GPT-5.5; GPT-5.6 Luna; GPT-5.6 Sol</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>bix-61-q5</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Claude Code, superseded); DeepSeek V4 Pro (Codex); GPT-5.5; GPT-5.6 Luna; GPT-5.6 Sol</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>bix-26-q5</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Claude Code, superseded); GPT-5.5; GPT-5.6 Luna; GPT-5.6 Sol</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>bix-54-q7</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Claude Code, superseded); GPT-5.5; GPT-5.6 Luna; GPT-5.6 Sol</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>bix-32-q2</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Codex)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>bix-43-q2</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Codex)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>d | As archived (archive table B2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>Model configuration</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>Execution condition</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>3/3 scored correct</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>1-2/3 scored correct</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="inlineStr">
+        <is>
+          <t>0/3 scored correct</t>
+        </is>
+      </c>
+      <c r="F45" s="9" t="inlineStr">
+        <is>
+          <t>At least one scored correct</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>GPT-5.5</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>Open-ended code</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>44/50 (88.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>GPT-5.5</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
         <is>
           <t>Galaxy</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>45/50 (90.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>GPT-5.6 Sol</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>Open-ended code</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>45/50 (90.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>GPT-5.6 Sol</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>Galaxy</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>45/50 (90.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>GPT-5.6 Luna</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>Open-ended code</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>46/50 (92.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>GPT-5.6 Luna</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>Galaxy</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>45/50 (90.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Codex)</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>Open-ended code</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>43/50 (86.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Codex)</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>Galaxy</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>45/50 (90.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Claude Code, superseded)</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>Open-ended code</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>42/50 (84.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Claude Code, superseded)</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>Galaxy</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D55" s="6" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="E55" s="6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F33" s="6" t="inlineStr">
+      <c r="F55" s="6" t="inlineStr">
         <is>
           <t>45/50 (90.0%)</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="10" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="10" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1">
-      <c r="A36" s="6" t="inlineStr">
+    <row r="58" ht="15" customHeight="1">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>Unanimous accuracy is the share of tasks whose three replicate runs were all scored correct (Supplementary Note 8).</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="24" customHeight="1">
-      <c r="A37" s="6" t="inlineStr">
+    <row r="59" ht="24" customHeight="1">
+      <c r="A59" s="6" t="inlineStr">
         <is>
           <t>Each row contains 50 task replicate sets; the middle three categories are mutually exclusive. At least one is an overlapping endpoint, not single-run accuracy. These are replicate-labelled archived runs, not best-of-three adaptive attempts.</t>
         </is>
@@ -48138,8 +48623,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A58:G58"/>
+    <mergeCell ref="A59:G59"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
